--- a/data_input/maiz_soil_params_rain_high.xlsx
+++ b/data_input/maiz_soil_params_rain_high.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dario_outputs\PyAEZ\data_input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{668A802E-CE3E-4C17-A6E5-890356599A07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ED681CC-EDA7-4ADB-99F0-31920C534EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" activeTab="6" xr2:uid="{8AAD9566-BB4C-44D2-B3CE-FD7B121B3AA5}"/>
   </bookViews>
@@ -1034,22 +1034,22 @@
         <v>10</v>
       </c>
       <c r="B1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C1">
+        <v>20</v>
+      </c>
+      <c r="D1">
+        <v>35</v>
+      </c>
+      <c r="E1">
+        <v>70</v>
+      </c>
+      <c r="F1">
         <v>85</v>
       </c>
-      <c r="D1">
-        <v>70</v>
-      </c>
-      <c r="E1">
-        <v>35</v>
-      </c>
-      <c r="F1">
-        <v>20</v>
-      </c>
       <c r="G1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -1057,22 +1057,22 @@
         <v>11</v>
       </c>
       <c r="B2">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="C2">
+        <v>30</v>
+      </c>
+      <c r="D2">
+        <v>50</v>
+      </c>
+      <c r="E2">
+        <v>70</v>
+      </c>
+      <c r="F2">
         <v>90</v>
       </c>
-      <c r="D2">
-        <v>70</v>
-      </c>
-      <c r="E2">
-        <v>50</v>
-      </c>
-      <c r="F2">
-        <v>30</v>
-      </c>
       <c r="G2">
-        <v>10</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -1640,22 +1640,22 @@
         <v>10</v>
       </c>
       <c r="B1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C1">
+        <v>20</v>
+      </c>
+      <c r="D1">
+        <v>35</v>
+      </c>
+      <c r="E1">
+        <v>70</v>
+      </c>
+      <c r="F1">
         <v>85</v>
       </c>
-      <c r="D1">
-        <v>70</v>
-      </c>
-      <c r="E1">
-        <v>35</v>
-      </c>
-      <c r="F1">
-        <v>20</v>
-      </c>
       <c r="G1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -1663,22 +1663,22 @@
         <v>11</v>
       </c>
       <c r="B2">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="C2">
+        <v>30</v>
+      </c>
+      <c r="D2">
+        <v>50</v>
+      </c>
+      <c r="E2">
+        <v>70</v>
+      </c>
+      <c r="F2">
         <v>90</v>
       </c>
-      <c r="D2">
-        <v>70</v>
-      </c>
-      <c r="E2">
-        <v>50</v>
-      </c>
-      <c r="F2">
-        <v>30</v>
-      </c>
       <c r="G2">
-        <v>10</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -1823,6 +1823,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008864D41C708CC54AABC64DB9F8EC5160" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8280e7c680d5d724f4413038ca100d1d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="aecedfd1-a701-4d39-be9b-da32a8dfc2a5" xmlns:ns3="6cc8ca2e-56d8-406d-8e41-68c6b727753a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a78283ead66d0e44d8e1b525c3947135" ns2:_="" ns3:_="">
     <xsd:import namespace="aecedfd1-a701-4d39-be9b-da32a8dfc2a5"/>
@@ -2065,16 +2074,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61D9B97E-2726-43EE-9F6F-AB0281F201DE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88016C37-4A20-47C0-B09F-CE1025F19C6C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2091,12 +2099,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61D9B97E-2726-43EE-9F6F-AB0281F201DE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>